--- a/input/Login.xlsx
+++ b/input/Login.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Mobile Automation _talntx\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC6C732-4FE9-4D12-A5D1-15A88B620034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5477CBA-B908-4E0B-B32E-42723B997544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="CELogin" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,25 +37,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>phoneNumber</t>
   </si>
   <si>
     <t>9025663147</t>
   </si>
+  <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>6382918880</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF5C92FF"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -77,9 +90,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,17 +431,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F873A05F-98AA-4B8C-BC99-F5F8F22A7373}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -433,4 +449,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4782DBBA-35AC-47FA-BFFB-240258B1C539}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/input/Login.xlsx
+++ b/input/Login.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5477CBA-B908-4E0B-B32E-42723B997544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2A7EFA-6989-4DF7-8B1C-FDC1E8FABACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
